--- a/dummy.xlsx
+++ b/dummy.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\notes\Data Analysis\online_DA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAC3B31-9A56-450A-8610-0C4E066F2680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC93EA97-7F8A-4C95-BAC1-BF7553184F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>name</t>
   </si>
@@ -70,6 +71,30 @@
   </si>
   <si>
     <t>oxana@gmail.com</t>
+  </si>
+  <si>
+    <t>sno</t>
+  </si>
+  <si>
+    <t>marks</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>aman</t>
+  </si>
+  <si>
+    <t>raman</t>
+  </si>
+  <si>
+    <t>sonia</t>
+  </si>
+  <si>
+    <t>kashish</t>
+  </si>
+  <si>
+    <t>anil</t>
   </si>
 </sst>
 </file>
@@ -493,4 +518,178 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E236877E-CFFD-4219-8C7A-23EC2AAAC09C}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>45</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3">
+        <v>63</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>75</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>85</v>
+      </c>
+      <c r="D7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11">
+        <v>65</v>
+      </c>
+      <c r="D11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>